--- a/daily_matches/job_matches_2026-10-05.xlsx
+++ b/daily_matches/job_matches_2026-10-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Data Engineer, Data Management &amp; BI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>La Familia Medical Center</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>S3, Glue, Athena, Redshift, Data Lake, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aacae00553886f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52dec15d92eb10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Data Analyst - Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, scikit-learn, Redshift, BigQuery, Dataflow, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00692c5e7383a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer III AI, Automation, &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, MySQL, NoSQL, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,112 +554,1092 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ada37471f3f9718</t>
+          <t>https://www.indeed.com/viewjob?jk=5b965769d33666ec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Hybrid Dallas, TX)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>RAG, S3, Glue, Data Lake, Kinesis, CI/CD, Terraform, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dd49e97edcf49f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad2431edc28d94e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Remote</t>
+          <t>DevOps Engineer (Infrastructure and Security Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Castle Rock Associates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, scikit-learn, XGBoost, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c79bcb39350ddea</t>
+          <t>https://www.indeed.com/viewjob?jk=be4fc165394860fd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>West Palm Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rancho Cordova, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GEI Consultants</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53183509479236f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Meso Scale Diagnostics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, OpenCV, Docker, CI/CD, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cc21eb6768cd9c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7be1b9b5bc867059</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software engineer 1 – AI/ML Engineer (MLOps)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PyTorch, scikit-learn, XGBoost, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d8388afd9a26b9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI &amp; Generative AI – Consultant / Architect / Engineer / Applied AI Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KT2i Inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c13d563a422d36c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst, Customer Analytics (Insurance)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57f5b67299fda823</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Widescope Consulting and Contracting Services</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f76ef0682c111cda</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=301410781a0cac86</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>USA - Tax - Other Tax - Americas Tax Technology Group (ATTG) - Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, AKS, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b976c1dd66e0b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, MicroStrategy, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfb83f62ec533f47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Stratus</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, Git, Kafka, MongoDB, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=188a89fdfdaeabd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UFP Industries, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96f2be2da8467d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Context Developer - Indiana</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RadCube</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, MLflow, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2709a45618a7f12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Computer Vision Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Azure ML, Docker, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17288af02a7922a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Solution Engineer – San Francisco</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0b116c9d6583fca</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Solution Engineer – FedRAMP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e506eb3504497f76</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Solution Engineer – FedRAMP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9409f03138428e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Solution Engineer – San Francisco</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=857f296ac3d1e028</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Solution Engineer – San Francisco</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a2f9ae71eb0105a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Solution Engineer – FedRAMP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b20ecd87390a9a9</t>
         </is>
       </c>
     </row>
